--- a/public/downloads/Sales-Data-2025.xlsx
+++ b/public/downloads/Sales-Data-2025.xlsx
@@ -1,47 +1,224 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sales" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sales" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="65">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>2025-01-05</t>
+  </si>
+  <si>
+    <t>Laptop Dell XPS 13</t>
+  </si>
+  <si>
+    <t>Kinh Doanh</t>
+  </si>
+  <si>
+    <t>2025-01-10</t>
+  </si>
+  <si>
+    <t>Chuot Logitech MX Master 3</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>Man hinh Samsung 27 inch IPS</t>
+  </si>
+  <si>
+    <t>Ky Thuat</t>
+  </si>
+  <si>
+    <t>2025-01-22</t>
+  </si>
+  <si>
+    <t>Ban phim co Keychron K2</t>
+  </si>
+  <si>
+    <t>Nhan Su</t>
+  </si>
+  <si>
+    <t>2025-02-03</t>
+  </si>
+  <si>
+    <t>Tai nghe Sony WH-1000XM5</t>
+  </si>
+  <si>
+    <t>2025-02-08</t>
+  </si>
+  <si>
+    <t>Ke Toan</t>
+  </si>
+  <si>
+    <t>2025-02-14</t>
+  </si>
+  <si>
+    <t>Webcam Logitech C920</t>
+  </si>
+  <si>
+    <t>2025-02-20</t>
+  </si>
+  <si>
+    <t>2025-03-01</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>2025-03-12</t>
+  </si>
+  <si>
+    <t>2025-03-18</t>
+  </si>
+  <si>
+    <t>2025-03-25</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>2025-04-09</t>
+  </si>
+  <si>
+    <t>2025-04-16</t>
+  </si>
+  <si>
+    <t>2025-04-23</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>2025-06-03</t>
+  </si>
+  <si>
+    <t>2025-06-10</t>
+  </si>
+  <si>
+    <t>2025-06-17</t>
+  </si>
+  <si>
+    <t>2025-06-24</t>
+  </si>
+  <si>
+    <t>2025-07-01</t>
+  </si>
+  <si>
+    <t>2025-07-08</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>2025-07-22</t>
+  </si>
+  <si>
+    <t>2025-07-29</t>
+  </si>
+  <si>
+    <t>2025-08-05</t>
+  </si>
+  <si>
+    <t>2025-08-12</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>2025-08-26</t>
+  </si>
+  <si>
+    <t>2025-09-02</t>
+  </si>
+  <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
+    <t>2025-09-16</t>
+  </si>
+  <si>
+    <t>2025-09-23</t>
+  </si>
+  <si>
+    <t>2025-10-01</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>2025-10-22</t>
+  </si>
+  <si>
+    <t>2025-10-29</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t>2025-11-19</t>
+  </si>
+  <si>
+    <t>2025-11-26</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,13 +242,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,726 +581,732 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D51"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Product</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Department</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Amount</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2025-01-05</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Laptop Dell XPS 13</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Kinh Doanh</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
       </c>
       <c r="D2">
         <v>25000000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2025-01-10</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Chuot Logitech MX Master 3</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Marketing</v>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
         <v>1850000</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2025-01-15</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Man hinh Samsung 27 inch IPS</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Ky Thuat</v>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
         <v>5500000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2025-01-22</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Ban phim co Keychron K2</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Nhan Su</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
       <c r="D5">
         <v>2200000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2025-02-03</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Tai nghe Sony WH-1000XM5</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Marketing</v>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
       </c>
       <c r="D6">
         <v>7500000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2025-02-08</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Laptop Dell XPS 13</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Ke Toan</v>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
       <c r="D7">
         <v>25000000</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2025-02-14</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Webcam Logitech C920</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Ky Thuat</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
       </c>
       <c r="D8">
         <v>1650000</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>2025-02-20</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Man hinh Samsung 27 inch IPS</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Kinh Doanh</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
       </c>
       <c r="D9">
         <v>5500000</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>2025-03-01</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Chuot Logitech MX Master 3</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Nhan Su</v>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
       </c>
       <c r="D10">
         <v>1850000</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2025-03-07</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Laptop Dell XPS 13</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Marketing</v>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
       </c>
       <c r="D11">
         <v>25000000</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>2025-03-12</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Ban phim co Keychron K2</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Ky Thuat</v>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
       </c>
       <c r="D12">
         <v>2200000</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2025-03-18</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Tai nghe Sony WH-1000XM5</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Ke Toan</v>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
       </c>
       <c r="D13">
         <v>7500000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2025-03-25</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Webcam Logitech C920</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Kinh Doanh</v>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
       </c>
       <c r="D14">
         <v>1650000</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>2025-04-02</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Man hinh Samsung 27 inch IPS</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Marketing</v>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
       </c>
       <c r="D15">
         <v>5500000</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2025-04-09</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Laptop Dell XPS 13</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Nhan Su</v>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
       </c>
       <c r="D16">
         <v>25000000</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2025-04-16</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Chuot Logitech MX Master 3</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Ky Thuat</v>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
       </c>
       <c r="D17">
         <v>1850000</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>2025-04-23</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Ban phim co Keychron K2</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Kinh Doanh</v>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
       </c>
       <c r="D18">
         <v>2200000</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>2025-05-05</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Tai nghe Sony WH-1000XM5</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Marketing</v>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
       </c>
       <c r="D19">
         <v>7500000</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>2025-05-12</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Webcam Logitech C920</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Ke Toan</v>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
       </c>
       <c r="D20">
         <v>1650000</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>2025-05-19</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Laptop Dell XPS 13</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Ky Thuat</v>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
       </c>
       <c r="D21">
         <v>25000000</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2025-05-26</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Man hinh Samsung 27 inch IPS</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Kinh Doanh</v>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
       </c>
       <c r="D22">
         <v>5500000</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>2025-06-03</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Chuot Logitech MX Master 3</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Nhan Su</v>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
       </c>
       <c r="D23">
         <v>1850000</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2025-06-10</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Ban phim co Keychron K2</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Marketing</v>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
       </c>
       <c r="D24">
         <v>2200000</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2025-06-17</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Tai nghe Sony WH-1000XM5</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Kinh Doanh</v>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
       </c>
       <c r="D25">
         <v>7500000</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2025-06-24</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Webcam Logitech C920</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Ky Thuat</v>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
       </c>
       <c r="D26">
         <v>1650000</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>2025-07-01</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Laptop Dell XPS 13</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Ke Toan</v>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
       </c>
       <c r="D27">
         <v>25000000</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>2025-07-08</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Man hinh Samsung 27 inch IPS</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Marketing</v>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
       </c>
       <c r="D28">
         <v>5500000</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>2025-07-15</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Chuot Logitech MX Master 3</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Ky Thuat</v>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
       </c>
       <c r="D29">
         <v>1850000</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>2025-07-22</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Ban phim co Keychron K2</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Nhan Su</v>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
       </c>
       <c r="D30">
         <v>2200000</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>2025-07-29</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Tai nghe Sony WH-1000XM5</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Kinh Doanh</v>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" t="s">
+        <v>6</v>
       </c>
       <c r="D31">
         <v>7500000</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>2025-08-05</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Webcam Logitech C920</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Marketing</v>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
       </c>
       <c r="D32">
         <v>1650000</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>2025-08-12</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Laptop Dell XPS 13</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Ky Thuat</v>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
       </c>
       <c r="D33">
         <v>50000000</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>2025-08-19</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Man hinh Samsung 27 inch IPS</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Ke Toan</v>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
       </c>
       <c r="D34">
         <v>11000000</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Ban phim co Keychron K2</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Kinh Doanh</v>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
       </c>
       <c r="D35">
         <v>4400000</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Tai nghe Sony WH-1000XM5</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Nhan Su</v>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
       </c>
       <c r="D36">
         <v>15000000</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>2025-09-09</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Chuot Logitech MX Master 3</v>
-      </c>
-      <c r="C37" t="str">
-        <v>Marketing</v>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
       </c>
       <c r="D37">
         <v>5550000</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>2025-09-16</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Webcam Logitech C920</v>
-      </c>
-      <c r="C38" t="str">
-        <v>Ky Thuat</v>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
       </c>
       <c r="D38">
         <v>4950000</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>2025-09-23</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Laptop Dell XPS 13</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Kinh Doanh</v>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
       </c>
       <c r="D39">
         <v>25000000</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>2025-10-01</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Man hinh Samsung 27 inch IPS</v>
-      </c>
-      <c r="C40" t="str">
-        <v>Marketing</v>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
       </c>
       <c r="D40">
         <v>5500000</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>2025-10-08</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Ban phim co Keychron K2</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Ke Toan</v>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
       </c>
       <c r="D41">
         <v>2200000</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>2025-10-15</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Tai nghe Sony WH-1000XM5</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Ky Thuat</v>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
       </c>
       <c r="D42">
         <v>7500000</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>2025-10-22</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Chuot Logitech MX Master 3</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Nhan Su</v>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
       </c>
       <c r="D43">
         <v>1850000</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>2025-10-29</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Webcam Logitech C920</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Kinh Doanh</v>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
       </c>
       <c r="D44">
         <v>1650000</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>2025-11-05</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Laptop Dell XPS 13</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Marketing</v>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
       </c>
       <c r="D45">
         <v>75000000</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>2025-11-12</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Man hinh Samsung 27 inch IPS</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Ky Thuat</v>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
       </c>
       <c r="D46">
         <v>16500000</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>2025-11-19</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Ban phim co Keychron K2</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Kinh Doanh</v>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
       </c>
       <c r="D47">
         <v>6600000</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>2025-11-26</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Tai nghe Sony WH-1000XM5</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Ke Toan</v>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
       </c>
       <c r="D48">
         <v>22500000</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>2025-12-03</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Chuot Logitech MX Master 3</v>
-      </c>
-      <c r="C49" t="str">
-        <v>Marketing</v>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
       </c>
       <c r="D49">
         <v>7400000</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>2025-12-10</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Webcam Logitech C920</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Nhan Su</v>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
       </c>
       <c r="D50">
         <v>6600000</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>2025-12-17</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Laptop Dell XPS 13</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Kinh Doanh</v>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
       </c>
       <c r="D51">
         <v>50000000</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>